--- a/SuppXLS/Scen_z_MACC-IND.xlsx
+++ b/SuppXLS/Scen_z_MACC-IND.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACCE82A9-FABA-4DC7-AAB5-C5A1E235B6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BAD5E6F-4F37-4679-A08F-7633B0D4B0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UCT2" sheetId="12" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -100,6 +101,33 @@
   <si>
     <t>FT-IND*,-FT-INDELC</t>
   </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>TimeSlice</t>
+  </si>
+  <si>
+    <t>Attrib_Cond</t>
+  </si>
+  <si>
+    <t>Val_Cond</t>
+  </si>
+  <si>
+    <t>Pset_PD</t>
+  </si>
+  <si>
+    <t>Cset_Set</t>
+  </si>
+  <si>
+    <t>Cset_CD</t>
+  </si>
+  <si>
+    <t>PRC_NOFF</t>
+  </si>
+  <si>
+    <t>2025-2050</t>
+  </si>
 </sst>
 </file>
 
@@ -116,7 +144,7 @@
     <numFmt numFmtId="169" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
     <numFmt numFmtId="170" formatCode="General_)"/>
   </numFmts>
-  <fonts count="61">
+  <fonts count="62">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -554,8 +582,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="54">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -833,8 +868,20 @@
         <fgColor indexed="55"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="44"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1056,6 +1103,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1706">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2875,7 +2933,7 @@
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2884,6 +2942,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="52" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="53" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="52" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1706">
     <cellStyle name="20% - Accent1" xfId="21" builtinId="30" customBuiltin="1"/>
@@ -4904,7 +4976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="11" max="11" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -4912,27 +4984,27 @@
     <col min="13" max="13" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:16">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:16">
       <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:16">
       <c r="J4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:16">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -4973,7 +5045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:16">
       <c r="B6" t="s">
         <v>15</v>
       </c>
@@ -5000,7 +5072,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:16">
       <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
@@ -5015,7 +5087,7 @@
         <v>0.22999999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:16">
       <c r="D8" t="s">
         <v>21</v>
       </c>
@@ -5029,7 +5101,7 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:16">
       <c r="D9" t="s">
         <v>21</v>
       </c>
@@ -5042,6 +5114,95 @@
       <c r="K9">
         <v>-0.77</v>
       </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="B13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" thickBot="1">
+      <c r="B14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="M14" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="N14" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="30">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8">
+        <v>1</v>
+      </c>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="23" type="noConversion"/>
@@ -5054,4 +5215,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8550708-D5DF-4939-8453-F10175C398BF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>